--- a/ZS_2026_vyuka/emv1/lab06/lab06_mereni.xlsx
+++ b/ZS_2026_vyuka/emv1/lab06/lab06_mereni.xlsx
@@ -183,6 +183,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -230,13 +231,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="6.75"/>
@@ -255,6 +250,11 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -317,10 +317,18 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -329,70 +337,76 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -459,10 +473,10 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFE97132"/>
+      <rgbColor rgb="FFFF420E"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF004586"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -480,41 +494,7 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Naměřená závislost ln(gamma) = f(1/T)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -586,20 +566,56 @@
           </c:dLbls>
           <c:yVal>
             <c:numRef>
-              <c:f>'Uloha 6'!$I$3:$I$15</c:f>
+              <c:f>'Uloha 6'!$I$4:$I$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2.24034572909645</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.11871084687861</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.048259185928</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.98685944046952</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.94301881564622</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.90301260538958</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.85566607881221</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.76557240467143</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7265996497067</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.71997179926432</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.65814317626278</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.61107154142135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="8105148"/>
-        <c:axId val="81605693"/>
+        <c:axId val="37265051"/>
+        <c:axId val="38771258"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="8105148"/>
+        <c:axId val="37265051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -678,12 +694,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81605693"/>
+        <c:crossAx val="38771258"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81605693"/>
+        <c:axId val="38771258"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -762,7 +778,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8105148"/>
+        <c:crossAx val="37265051"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -825,6 +841,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.108631789486843"/>
+          <c:y val="0.0457273030336704"/>
+          <c:w val="0.623038939933746"/>
+          <c:h val="0.91576841871319"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -833,44 +860,48 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Uloha 6'!$A$2</c:f>
+              <c:f>'Uloha 6'!$E$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>t [°C]</c:v>
+                  <c:v>ln(gamma_i)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="156082"/>
+              <a:srgbClr val="004586"/>
             </a:solidFill>
-            <a:ln w="38160">
+            <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="156082"/>
+                <a:srgbClr val="004586"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -880,7 +911,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="38160">
+                <a:ln w="28800">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -893,60 +924,273 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:xVal>
+            <c:strRef>
+              <c:f>'Uloha 6'!$D$23:$D$33</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0,002363</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0,002231</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0,002113</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0,002007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0,001911</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0,001824</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0,001745</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0,001672</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0,001605</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0,001543</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0,001486</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Uloha 6'!$I$3:$I$15</c:f>
+              <c:f>'Uloha 6'!$E$23:$E$33</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-1.60227518943124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.753207417084811</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.00613534497456305</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.689261830605213</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.30709858235164</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.86857879375815</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.38107704482213</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.85073501743889</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.28270880706467</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.68135899955816</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.05039839263892</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
+        <c:axId val="31772182"/>
+        <c:axId val="14028247"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="31772182"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="14028247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="14028247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31772182"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="span"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="0"/>
+          <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Uloha 6'!$A$2</c:f>
+              <c:f>'Uloha 6'!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>t [°C]</c:v>
+                  <c:v>ln(gamma)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="e97132"/>
+              <a:srgbClr val="004586"/>
             </a:solidFill>
-            <a:ln w="38160">
+            <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="004586"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -956,7 +1200,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="38160">
+                <a:ln w="28800">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -969,6 +1213,259 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="0">
+                <a:solidFill>
+                  <a:srgbClr val="004586"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="0"/>
+            <c:backward val="17"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Uloha 6'!$H$3:$H$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.00341122292341805</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0032986970146792</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.00319335781574325</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.00309453814018258</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0030016509079994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.00291417747340813</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.00283165793572137</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.00275368305108082</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.00267988744472732</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00260994388620645</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00254355843825512</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0024804663276696</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0024204284158296</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Uloha 6'!$I$3:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="1">
+                  <c:v>2.24034572909645</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.11871084687861</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.048259185928</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.98685944046952</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.94301881564622</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.90301260538958</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.85566607881221</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.76557240467143</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7265996497067</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.71997179926432</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.65814317626278</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.61107154142135</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Uloha 6'!$E$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ln(gamma_i)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="diamond"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="ff420e"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Uloha 6'!$D$23:$D$33</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.00236322816967978</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.00223139573803414</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.00211349466342598</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.00200742748168222</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.00191149765841537</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.00182431816108729</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.00174474395882404</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0016718214494692</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.00160475006017813</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00154285273470647</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00148555299710317</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'Uloha 6'!$E$23:$E$33</c:f>
@@ -1011,73 +1508,27 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="79349533"/>
-        <c:axId val="95131474"/>
+        <c:axId val="10168362"/>
+        <c:axId val="98385308"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="79349533"/>
+        <c:axId val="10168362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="cccccc"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="825" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                    <a:ea typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>1/T [K^-1]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="12600">
+          <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="8b8b8b"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
-            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1085,23 +1536,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="675" b="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95131474"/>
+        <c:crossAx val="98385308"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95131474"/>
+        <c:axId val="98385308"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1109,59 +1556,22 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
+            <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="cccccc"/>
+                <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="825" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                    <a:ea typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>ln(gamma) [-]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="12600">
+          <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="8b8b8b"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
-            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1169,42 +1579,57 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="675" b="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79349533"/>
+        <c:crossAx val="10168362"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="span"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
+    <a:ln w="0">
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -1220,10 +1645,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>610920</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>179280</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1232,7 +1657,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9996120" y="2095560"/>
-        <a:ext cx="6910920" cy="3047040"/>
+        <a:ext cx="5256000" cy="3678840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1244,29 +1669,59 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>693000</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>18360</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>105120</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>353520</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:colOff>177840</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>47520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvPr id="2" name=""/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6130440" y="3447360"/>
-        <a:ext cx="9907560" cy="4933800"/>
+        <a:off x="10101240" y="5952960"/>
+        <a:ext cx="5761080" cy="3238560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>856800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>59400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>680760</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="21584400">
+        <a:off x="856800" y="8250840"/>
+        <a:ext cx="8221680" cy="4643640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1452,888 +1907,942 @@
   <dimension ref="A1:M43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <f aca="false">A3+273.15</f>
         <v>293.15</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5" t="e">
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="e">
         <f aca="false">C3/(D3/1000)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F3" s="5" t="e">
+      <c r="F3" s="6" t="e">
         <f aca="false">E3*$L$10/$L$9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G3" s="5" t="e">
+      <c r="G3" s="6" t="e">
         <f aca="false">1/F3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <f aca="false">1/B3</f>
         <v>0.00341122292341805</v>
       </c>
-      <c r="I3" s="7" t="e">
+      <c r="I3" s="8" t="e">
         <f aca="false">LN(G3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="8" t="n">
+      <c r="L3" s="9" t="n">
         <v>1.602E-019</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <f aca="false">A4+273.15</f>
         <v>303.15</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5" t="e">
+      <c r="C4" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.62753</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <f aca="false">C4/(D4/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F4" s="5" t="e">
+        <v>252.258856150304</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <f aca="false">E4*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="5" t="e">
+        <v>0.106421704938409</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <f aca="false">1/F4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H4" s="6" t="n">
+        <v>9.39657939683208</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <f aca="false">1/B4</f>
         <v>0.0032986970146792</v>
       </c>
-      <c r="I4" s="7" t="e">
+      <c r="I4" s="8" t="n">
         <f aca="false">LN(G4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K4" s="8" t="s">
+        <v>2.24034572909645</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="9" t="n">
         <v>2.8E+025</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <f aca="false">A5+273.15</f>
         <v>313.15</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5" t="e">
+      <c r="C5" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.55566</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <f aca="false">C5/(D5/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="5" t="e">
+        <v>284.886441349026</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <f aca="false">E5*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="5" t="e">
+        <v>0.120186467444121</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <f aca="false">1/F5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H5" s="6" t="n">
+        <v>8.32040429564119</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <f aca="false">1/B5</f>
         <v>0.00319335781574325</v>
       </c>
-      <c r="I5" s="7" t="e">
+      <c r="I5" s="8" t="n">
         <f aca="false">LN(G5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K5" s="8" t="s">
+        <v>2.11871084687861</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="9" t="n">
         <v>0.135</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <f aca="false">A6+273.15</f>
         <v>323.15</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5" t="e">
+      <c r="C6" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.51786</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <f aca="false">C6/(D6/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F6" s="5" t="e">
+        <v>305.68107210443</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <f aca="false">E6*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="5" t="e">
+        <v>0.128959202294056</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <f aca="false">1/F6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H6" s="6" t="n">
+        <v>7.75439039797852</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <f aca="false">1/B6</f>
         <v>0.00309453814018258</v>
       </c>
-      <c r="I6" s="7" t="e">
+      <c r="I6" s="8" t="n">
         <f aca="false">LN(G6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K6" s="8" t="s">
+        <v>2.048259185928</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="9" t="n">
         <v>0.048</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <f aca="false">A7+273.15</f>
         <v>333.15</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5" t="e">
+      <c r="C7" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <f aca="false">C7/(D7/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="5" t="e">
+        <v>325.037986119667</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <f aca="false">E7*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="5" t="e">
+        <v>0.137125400394234</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <f aca="false">1/F7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H7" s="6" t="n">
+        <v>7.29259493226644</v>
+      </c>
+      <c r="H7" s="7" t="n">
         <f aca="false">1/B7</f>
         <v>0.0030016509079994</v>
       </c>
-      <c r="I7" s="7" t="e">
+      <c r="I7" s="8" t="n">
         <f aca="false">LN(G7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K7" s="8" t="s">
+        <v>1.98685944046952</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="9" t="n">
         <v>1.11</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <f aca="false">A8+273.15</f>
         <v>343.15</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5" t="e">
+      <c r="C8" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <f aca="false">C8/(D8/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F8" s="5" t="e">
+        <v>339.604831270247</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <f aca="false">E8*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="5" t="e">
+        <v>0.143270788192135</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <f aca="false">1/F8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H8" s="6" t="n">
+        <v>6.97978989728832</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <f aca="false">1/B8</f>
         <v>0.00291417747340813</v>
       </c>
-      <c r="I8" s="7" t="e">
+      <c r="I8" s="8" t="n">
         <f aca="false">LN(G8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="8" t="s">
+        <v>1.94301881564622</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="9" t="n">
         <v>8.617333262E-005</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <f aca="false">A9+273.15</f>
         <v>353.15</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5" t="e">
+      <c r="C9" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <f aca="false">C9/(D9/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F9" s="5" t="e">
+        <v>353.466562465111</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <f aca="false">E9*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="5" t="e">
+        <v>0.149118706039969</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <f aca="false">1/F9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H9" s="6" t="n">
+        <v>6.70606677429167</v>
+      </c>
+      <c r="H9" s="7" t="n">
         <f aca="false">1/B9</f>
         <v>0.00283165793572137</v>
       </c>
-      <c r="I9" s="7" t="e">
+      <c r="I9" s="8" t="n">
         <f aca="false">LN(G9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="8" t="s">
+        <v>1.90301260538958</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="L9" s="9" t="n">
         <v>0.016</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <f aca="false">A10+273.15</f>
         <v>363.15</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5" t="e">
+      <c r="C10" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <f aca="false">C10/(D10/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F10" s="5" t="e">
+        <v>370.604485648733</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <f aca="false">E10*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="5" t="e">
+        <v>0.156348767383059</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <f aca="false">1/F10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H10" s="6" t="n">
+        <v>6.39595704358812</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <f aca="false">1/B10</f>
         <v>0.00275368305108082</v>
       </c>
-      <c r="I10" s="7" t="e">
+      <c r="I10" s="8" t="n">
         <f aca="false">LN(G10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="8" t="s">
+        <v>1.85566607881221</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="9" t="n">
         <v>6.75E-006</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <f aca="false">A11+273.15</f>
         <v>373.15</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5" t="e">
+      <c r="C11" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <f aca="false">C11/(D11/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F11" s="5" t="e">
+        <v>405.543884818363</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <f aca="false">E11*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G11" s="5" t="e">
+        <v>0.171088826407747</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <f aca="false">1/F11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H11" s="6" t="n">
+        <v>5.84491705856204</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <f aca="false">1/B11</f>
         <v>0.00267988744472732</v>
       </c>
-      <c r="I11" s="7" t="e">
+      <c r="I11" s="8" t="n">
         <f aca="false">LN(G11)</f>
-        <v>#DIV/0!</v>
+        <v>1.76557240467143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <f aca="false">A12+273.15</f>
         <v>383.15</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5" t="e">
+      <c r="C12" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="E12" s="6" t="n">
         <f aca="false">C12/(D12/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F12" s="5" t="e">
+        <v>421.66107293165</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <f aca="false">E12*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="5" t="e">
+        <v>0.17788826514304</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <f aca="false">1/F12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H12" s="6" t="n">
+        <v>5.62150628202429</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <f aca="false">1/B12</f>
         <v>0.00260994388620645</v>
       </c>
-      <c r="I12" s="7" t="e">
+      <c r="I12" s="8" t="n">
         <f aca="false">LN(G12)</f>
-        <v>#DIV/0!</v>
+        <v>1.7265996497067</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <f aca="false">A13+273.15</f>
         <v>393.15</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5" t="e">
+      <c r="C13" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <f aca="false">C13/(D13/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F13" s="5" t="e">
+        <v>424.465061403979</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <f aca="false">E13*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="5" t="e">
+        <v>0.179071197779804</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <f aca="false">1/F13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H13" s="6" t="n">
+        <v>5.58437097868557</v>
+      </c>
+      <c r="H13" s="7" t="n">
         <f aca="false">1/B13</f>
         <v>0.00254355843825512</v>
       </c>
-      <c r="I13" s="7" t="e">
+      <c r="I13" s="8" t="n">
         <f aca="false">LN(G13)</f>
-        <v>#DIV/0!</v>
+        <v>1.71997179926432</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <f aca="false">A14+273.15</f>
         <v>403.15</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5" t="e">
+      <c r="C14" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <f aca="false">C14/(D14/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F14" s="5" t="e">
+        <v>451.537452222032</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <f aca="false">E14*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="5" t="e">
+        <v>0.19049236265617</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <f aca="false">1/F14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H14" s="6" t="n">
+        <v>5.24955429213168</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <f aca="false">1/B14</f>
         <v>0.0024804663276696</v>
       </c>
-      <c r="I14" s="7" t="e">
+      <c r="I14" s="8" t="n">
         <f aca="false">LN(G14)</f>
-        <v>#DIV/0!</v>
+        <v>1.65814317626278</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <f aca="false">A15+273.15</f>
         <v>413.15</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5" t="e">
+      <c r="C15" s="5" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <f aca="false">C15/(D15/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="5" t="e">
+        <v>473.300245171321</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <f aca="false">E15*$L$10/$L$9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="5" t="e">
+        <v>0.199673540931651</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <f aca="false">1/F15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H15" s="6" t="n">
+        <v>5.00817482043003</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <f aca="false">1/B15</f>
         <v>0.0024204284158296</v>
       </c>
-      <c r="I15" s="7" t="e">
+      <c r="I15" s="8" t="n">
         <f aca="false">LN(G15)</f>
-        <v>#DIV/0!</v>
+        <v>1.61107154142135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="9" t="e">
-        <f aca="false">AVERAGE(G3:G9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C18" s="0" t="s">
+      <c r="B18" s="10" t="n">
+        <f aca="false">AVERAGE(G4:G9)</f>
+        <v>7.74163761571637</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="0" t="e">
+      <c r="B19" s="1" t="n">
         <f aca="false">B18/($L$3*$L$5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C19" s="0" t="s">
+        <v>3.57961696754814E+020</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <f aca="false">A23+273.15</f>
         <v>423.15</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B23))</f>
         <v>0.201437687331975</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <f aca="false">1/B23</f>
         <v>0.00236322816967978</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="8" t="n">
         <f aca="false">LN(C23)</f>
         <v>-1.60227518943124</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <f aca="false">A24+273.15</f>
         <v>448.15</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B24))</f>
         <v>0.470853903335019</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <f aca="false">1/B24</f>
         <v>0.00223139573803414</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="8" t="n">
         <f aca="false">LN(C24)</f>
         <v>-0.753207417084811</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <f aca="false">A25+273.15</f>
         <v>473.15</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B25))</f>
         <v>1.00615420475423</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <f aca="false">1/B25</f>
         <v>0.00211349466342598</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="8" t="n">
         <f aca="false">LN(C25)</f>
         <v>0.00613534497456305</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <f aca="false">A26+273.15</f>
         <v>498.15</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B26))</f>
         <v>1.99224437650277</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <f aca="false">1/B26</f>
         <v>0.00200742748168222</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="8" t="n">
         <f aca="false">LN(C26)</f>
         <v>0.689261830605213</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <f aca="false">A27+273.15</f>
         <v>523.15</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B27))</f>
         <v>3.69543613901848</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <f aca="false">1/B27</f>
         <v>0.00191149765841537</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="8" t="n">
         <f aca="false">LN(C27)</f>
         <v>1.30709858235164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <f aca="false">A28+273.15</f>
         <v>548.15</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B28))</f>
         <v>6.47908174146069</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <f aca="false">1/B28</f>
         <v>0.00182431816108729</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="8" t="n">
         <f aca="false">LN(C28)</f>
         <v>1.86857879375815</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <f aca="false">A29+273.15</f>
         <v>573.15</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B29))</f>
         <v>10.8165464978467</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <f aca="false">1/B29</f>
         <v>0.00174474395882404</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="8" t="n">
         <f aca="false">LN(C29)</f>
         <v>2.38107704482213</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>325</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <f aca="false">A30+273.15</f>
         <v>598.15</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B30))</f>
         <v>17.3004933327122</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <f aca="false">1/B30</f>
         <v>0.0016718214494692</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="8" t="n">
         <f aca="false">LN(C30)</f>
         <v>2.85073501743889</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <f aca="false">A31+273.15</f>
         <v>623.15</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B31))</f>
         <v>26.6478589304792</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <f aca="false">1/B31</f>
         <v>0.00160475006017813</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="8" t="n">
         <f aca="false">LN(C31)</f>
         <v>3.28270880706467</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <f aca="false">A32+273.15</f>
         <v>648.15</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B32))</f>
         <v>39.7003101322524</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <f aca="false">1/B32</f>
         <v>0.00154285273470647</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="8" t="n">
         <f aca="false">LN(C32)</f>
         <v>3.68135899955816</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <f aca="false">A33+273.15</f>
         <v>673.15</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <f aca="false">$L$3*$L$4*($L$5+$L$6)*EXP(-$L$7/(2*$L$8*B33))</f>
         <v>57.4203283253983</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <f aca="false">1/B33</f>
         <v>0.00148555299710317</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="8" t="n">
         <f aca="false">LN(C33)</f>
         <v>4.05039839263892</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="0" t="s">
+      <c r="B36" s="12" t="n">
+        <v>0.001911</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="0" t="e">
+      <c r="B37" s="1" t="n">
         <f aca="false">1/B36</f>
-        <v>#DIV/0!</v>
+        <v>523.286237571952</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="0" t="e">
+      <c r="B38" s="1" t="n">
         <f aca="false">B37-273.15</f>
-        <v>#DIV/0!</v>
+        <v>250.136237571952</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="14" t="e">
+      <c r="B41" s="15" t="n">
         <f aca="false">$L$7/(2*$L$8*LN(($L$3*$L$4*($L$5+$L$6))/$B$18))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C41" s="15" t="s">
+        <v>556.583615329452</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="14" t="e">
+      <c r="B42" s="15" t="n">
         <f aca="false">B41-273.15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C42" s="15" t="s">
+        <v>283.433615329452</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="15"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
